--- a/TheCoffeeCream/api/TheCoffeeCream DB.xlsx
+++ b/TheCoffeeCream/api/TheCoffeeCream DB.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="570">
   <si>
     <t>Id</t>
   </si>
@@ -1450,13 +1450,13 @@
     <t>Note</t>
   </si>
   <si>
-    <t>4c447211-3b63-4512-af8a-d432a1254761</t>
-  </si>
-  <si>
-    <t>4703b039-4dba-4d14-9b67-b53b427ee844</t>
-  </si>
-  <si>
-    <t>2026-01-22T20:15:32.4008042+00:00</t>
+    <t>d369ce93-a94e-4309-8ebd-5a4a48f50223</t>
+  </si>
+  <si>
+    <t>eba284e9-7242-423a-9311-1c44eaaa791e</t>
+  </si>
+  <si>
+    <t>2026-01-31T14:42:59.0000000+00:00</t>
   </si>
   <si>
     <t>DINE_IN</t>
@@ -1465,328 +1465,121 @@
     <t>CASH</t>
   </si>
   <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
-    <t>a05aa4c4-bb3c-4e5e-b9a6-057a5fd06e64</t>
+    <t>FIXED</t>
   </si>
   <si>
     <t>SUCCESS</t>
   </si>
   <si>
-    <t>8fb61227-6054-4976-80fd-c0be160d01b3</t>
-  </si>
-  <si>
-    <t>0c95f6ee-2d89-442e-befc-82c6c87f6c37</t>
-  </si>
-  <si>
-    <t>eb633e2c-c5eb-4ff3-8d82-b2d51c3f6b26</t>
-  </si>
-  <si>
-    <t>901a4b6e-b667-4374-b9f7-a590365cf555</t>
-  </si>
-  <si>
-    <t>97d2cb61-19d5-4e8d-a5d1-9ed30e49fbb9</t>
-  </si>
-  <si>
-    <t>a1dc7d2c-cf83-4a15-9129-c4e653d0560a</t>
-  </si>
-  <si>
-    <t>20e7f24c-bb73-4f2e-bc61-ffbfffff1917</t>
-  </si>
-  <si>
-    <t>94e7aa9e-bfe0-4fcb-a8e5-7d58641b63fc</t>
-  </si>
-  <si>
-    <t>f51f98b7-debf-47fa-bd9b-95b476fa1666</t>
-  </si>
-  <si>
-    <t>8c000d15-bbd0-48ca-ac53-88c1321c35f2</t>
-  </si>
-  <si>
-    <t>86c64950-ae3e-4420-97b3-3deba3e033a8</t>
-  </si>
-  <si>
-    <t>fde3ac71-6caf-4fdc-a8e9-d0f7f8aec57e</t>
-  </si>
-  <si>
-    <t>e0f13920-cf82-4a93-aab2-09800c69bf5b</t>
-  </si>
-  <si>
-    <t>2026-01-23T05:07:51.7243579+00:00</t>
-  </si>
-  <si>
-    <t>COMBINED</t>
-  </si>
-  <si>
-    <t>Duy áo cưới</t>
-  </si>
-  <si>
-    <t>e2475a2a-1bc9-48dc-b66f-0c3c5f8f3919</t>
-  </si>
-  <si>
-    <t>2f694bce-3087-4ea0-9b52-7d104807778d</t>
-  </si>
-  <si>
-    <t>3d54ef2f-a94f-46cf-a508-33722534a7be</t>
-  </si>
-  <si>
-    <t>6291bcd1-7cb8-4981-bba3-207b94b65fba</t>
-  </si>
-  <si>
-    <t>9deb60a1-0afd-4516-b52e-1e36ced4629c</t>
-  </si>
-  <si>
-    <t>7a95ef42-1022-4436-b76b-3dd766a78dc4</t>
-  </si>
-  <si>
-    <t>828be22f-9575-4315-8c8d-f5c73d5016a2</t>
-  </si>
-  <si>
-    <t>fb4a9686-52a2-435e-ab78-71e872a2a5d7</t>
-  </si>
-  <si>
-    <t>2026-01-24T07:54:05.5119858+00:00</t>
-  </si>
-  <si>
-    <t>bce4f5c2-64c3-461b-8fb9-0f506fd798cf</t>
-  </si>
-  <si>
-    <t>f4918489-8f22-4d12-a48b-d022c51d0b08</t>
-  </si>
-  <si>
-    <t>2026-01-24T08:26:27.9422184+00:00</t>
-  </si>
-  <si>
-    <t>9d178994-ef97-43a1-9c64-d72d84bb304a</t>
-  </si>
-  <si>
-    <t>24c98eb5-2a88-4446-b385-c4d7cc73f57b</t>
-  </si>
-  <si>
-    <t>2026-01-24T12:50:39.7456853+00:00</t>
-  </si>
-  <si>
-    <t>672c52f3-2841-4699-818f-575263756cc4</t>
-  </si>
-  <si>
-    <t>918b2e27-d016-4a41-99ad-823bbccb2f02</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:16:29.3823065+00:00</t>
-  </si>
-  <si>
-    <t>47f4479a-4cb5-4f64-ba35-42a8d89ec249</t>
-  </si>
-  <si>
-    <t>cf542fde-0adf-4c5e-b2f8-573006d8bcdd</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:27:14.1514102+00:00</t>
-  </si>
-  <si>
-    <t>d91a1621-eac6-4704-9f02-5c22661b5782</t>
-  </si>
-  <si>
-    <t>3a5a776e-7c6d-4193-a50f-43da72e05a8c</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:27:18.8592815+00:00</t>
-  </si>
-  <si>
-    <t>b2b3189b-8cd5-4fe3-8068-49a865d1c351</t>
-  </si>
-  <si>
-    <t>d0aa388c-eab4-4cfa-b4bb-ba351042166e</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:27:29.4602934+00:00</t>
+    <t>5023276e-e38f-45fb-b82f-6aad4abb5c84</t>
+  </si>
+  <si>
+    <t>674390a7-d2ce-4772-9ed7-868f702ee0de</t>
+  </si>
+  <si>
+    <t>2026-02-01T02:51:36.4756926+00:00</t>
+  </si>
+  <si>
+    <t>1b64331b-0eb7-462f-bbaf-170c5cc41866</t>
+  </si>
+  <si>
+    <t>9330ac5c-2f14-43f6-87e2-853050e92ea4</t>
+  </si>
+  <si>
+    <t>2026-02-01T02:52:06.2679971+00:00</t>
+  </si>
+  <si>
+    <t>e65f17fc-d1c0-4856-91d3-fdbcb8e65fe9</t>
+  </si>
+  <si>
+    <t>17326de9-b394-4ccf-8e46-4f5bce5e8db7</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:10:12.2940465+00:00</t>
+  </si>
+  <si>
+    <t>f01f0f26-1163-4d94-8a28-2877d7f08678</t>
+  </si>
+  <si>
+    <t>219dd05a-6b27-4495-b7a3-953a7960aff6</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:10:31.1470379+00:00</t>
+  </si>
+  <si>
+    <t>48018d15-0ef5-40bb-ba37-8c6b574ef11d</t>
+  </si>
+  <si>
+    <t>68f785c6-e67a-483a-b3b9-76a7967d8d94</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:10:59.8470010+00:00</t>
+  </si>
+  <si>
+    <t>0bc99059-430e-43f4-a8ee-e498634b7354</t>
+  </si>
+  <si>
+    <t>ad229094-bc9c-4a51-bd2d-f3e9aacf9960</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:11:09.5836898+00:00</t>
+  </si>
+  <si>
+    <t>b94061e9-d7f8-41a4-8fce-b4083d48d923</t>
+  </si>
+  <si>
+    <t>7a7a41bc-4554-42c3-9405-231998299ab3</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:11:19.9475490+00:00</t>
   </si>
   <si>
     <t>TRANSFER</t>
   </si>
   <si>
-    <t>4a6c288c-1c83-494f-960a-bd6e8c6e304e</t>
-  </si>
-  <si>
-    <t>025aa07d-8a7d-4102-996e-4ff850bcbe22</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:33:30.5514018+00:00</t>
-  </si>
-  <si>
-    <t>0bfce639-b9c8-4f3c-ba4e-9001466f4f14</t>
-  </si>
-  <si>
-    <t>5f5ab809-4a5a-4a9d-a09d-4cb73ec177a7</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:37:40.5843855+00:00</t>
-  </si>
-  <si>
-    <t>da7e093d-6f09-4e9d-b17f-36edaae542eb</t>
-  </si>
-  <si>
-    <t>e0f96f4a-3dcc-4166-8843-0dd6bc92d276</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:50:24.0137345+00:00</t>
-  </si>
-  <si>
-    <t>Tes note</t>
-  </si>
-  <si>
-    <t>4a9ba5c7-f219-490d-a7dd-ab5f52a66199</t>
-  </si>
-  <si>
-    <t>86ccba1d-af00-4a40-a0ec-fae291a9151a</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:50:39.3193400+00:00</t>
-  </si>
-  <si>
-    <t>e3d4cec2-f6a1-4531-80fe-0b093fb2fb32</t>
-  </si>
-  <si>
-    <t>975099cd-1d94-47bb-9c7a-f3b7e1969e21</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:52:55.4483308+00:00</t>
-  </si>
-  <si>
-    <t>55aee999-431f-499c-ac67-e6198136a717</t>
-  </si>
-  <si>
-    <t>a4421488-777c-44e3-b9e4-53e154bfd7fd</t>
-  </si>
-  <si>
-    <t>2026-01-24T13:57:33.6045077+00:00</t>
-  </si>
-  <si>
-    <t>1ea213eb-9937-4258-be28-62c9f51af6eb</t>
-  </si>
-  <si>
-    <t>2ad3cbe8-b01f-4ebe-8f87-b1f775bb3815</t>
-  </si>
-  <si>
-    <t>2026-01-24T14:16:19.6798070+00:00</t>
-  </si>
-  <si>
-    <t>70ab4242-23f9-4afc-8519-2db03800e485</t>
-  </si>
-  <si>
-    <t>9f0c8c23-0b88-4473-8aae-bb4894d840dd</t>
-  </si>
-  <si>
-    <t>2026-01-24T19:27:13.9817748+00:00</t>
-  </si>
-  <si>
-    <t>bf8467c7-454e-4d2f-b26c-bf0c4dc2a49d</t>
-  </si>
-  <si>
-    <t>b0fe5896-5276-479b-ba68-88016b2f360c</t>
-  </si>
-  <si>
-    <t>2026-01-24T20:15:08.6821213+00:00</t>
-  </si>
-  <si>
-    <t>22f70c7c-2e8f-41f9-a5e8-01543ed29d4e</t>
-  </si>
-  <si>
-    <t>37e47c57-700b-401e-99ec-2cabda810346</t>
-  </si>
-  <si>
-    <t>2026-01-24T20:15:20.7433882+00:00</t>
-  </si>
-  <si>
-    <t>f52b511c-9545-4058-8004-e4605fd26ca6</t>
-  </si>
-  <si>
-    <t>8ebb3722-82ee-4e8f-ae80-e7fc5832335d</t>
-  </si>
-  <si>
-    <t>2026-01-24T20:33:44.1261588+00:00</t>
-  </si>
-  <si>
-    <t>16ffc02a-fd68-48a4-b1a0-6c4975041542</t>
-  </si>
-  <si>
-    <t>ac6e88e2-c42e-48ed-b561-7b14709fb3f8</t>
-  </si>
-  <si>
-    <t>2026-01-25T05:12:14.7860231+00:00</t>
-  </si>
-  <si>
-    <t>5319fc5a-2bc1-45a4-a02e-60af14932178</t>
-  </si>
-  <si>
-    <t>eba284e9-7242-423a-9311-1c44eaaa791e</t>
-  </si>
-  <si>
-    <t>2026-01-25T05:23:50.0432453+00:00</t>
-  </si>
-  <si>
-    <t>47706816-0114-42aa-bbf7-6c5ea879538d</t>
-  </si>
-  <si>
-    <t>c1c9fee8-ee2b-4c1a-bb0c-39a0d0ed41d7</t>
-  </si>
-  <si>
-    <t>2026-01-25T05:42:27.9550435+00:00</t>
-  </si>
-  <si>
-    <t>5d535602-2219-410c-a48c-61a5a418c171</t>
-  </si>
-  <si>
-    <t>7b6ad060-9491-4e0e-9657-582df2b2a287</t>
-  </si>
-  <si>
-    <t>2026-01-25T06:58:29.7975129+00:00</t>
-  </si>
-  <si>
-    <t>aa0e28b7-0e3d-4bf6-81cd-4f1016007585</t>
-  </si>
-  <si>
-    <t>c7e1c2f4-f714-443b-ab33-9c736ec1e500</t>
-  </si>
-  <si>
-    <t>2026-01-25T12:26:55.8435970+00:00</t>
-  </si>
-  <si>
-    <t>7843bd3d-0a50-4485-99b2-5f59a7678d3b</t>
-  </si>
-  <si>
-    <t>e121f99f-3fbc-4982-b2cc-d9e6ec5d2a22</t>
-  </si>
-  <si>
-    <t>2026-01-25T14:32:36.7421962+00:00</t>
-  </si>
-  <si>
-    <t>ef60dad2-450c-4e69-bd52-d8f236b6bcac</t>
-  </si>
-  <si>
-    <t>3fc99a64-4459-4926-9618-cf461313212d</t>
-  </si>
-  <si>
-    <t>2026-01-25T16:52:25.0549897+00:00</t>
-  </si>
-  <si>
-    <t>fe4f6429-d64c-49d0-be64-2e60c3ead5db</t>
-  </si>
-  <si>
-    <t>d5331fd0-edd6-4c9a-bfae-ff16e465044f</t>
-  </si>
-  <si>
-    <t>2026-01-25T16:53:05.4954062+00:00</t>
-  </si>
-  <si>
-    <t>fe86fca1-802b-4bc9-a589-80bf09c03cc3</t>
-  </si>
-  <si>
-    <t>718a2f65-eb25-49dd-81fd-df42ee600ae7</t>
-  </si>
-  <si>
-    <t>2026-01-31T14:18:05.1729143+00:00</t>
+    <t>5a1bdc7a-d97e-4dcf-96c5-34d9bbc13f36</t>
+  </si>
+  <si>
+    <t>b7e65632-fecd-401d-baf1-a17c8aba290b</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:11:54.3093889+00:00</t>
+  </si>
+  <si>
+    <t>2dfe3322-f5e8-4dc0-9e50-4ff930eaf036</t>
+  </si>
+  <si>
+    <t>ab0b5752-a808-4ba8-8355-272e0ef28080</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:12:55.3859409+00:00</t>
+  </si>
+  <si>
+    <t>af45f7e3-71cd-4203-8218-f33db17cf37f</t>
+  </si>
+  <si>
+    <t>75c1f412-0dd6-4035-b324-0c3eeb9e83dc</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:13:07.0091873+00:00</t>
+  </si>
+  <si>
+    <t>79511ba5-3a1d-4554-adbb-98db3022b5d4</t>
+  </si>
+  <si>
+    <t>da2e20bb-ab4d-4aaf-ba42-f709b3d8c0e5</t>
+  </si>
+  <si>
+    <t>2026-02-02T12:34:28.0000000+07:00</t>
+  </si>
+  <si>
+    <t>88040bdc-861d-4418-aa55-f254a7a2525b</t>
+  </si>
+  <si>
+    <t>d05e146b-b3d6-47c0-9a49-052d684d35b4</t>
+  </si>
+  <si>
+    <t>2026-02-02T06:43:45.9416375+00:00</t>
   </si>
   <si>
     <t>OrderId</t>
@@ -1801,25 +1594,103 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>409b1750-5b8e-40b7-8541-24aa6f2092b8</t>
-  </si>
-  <si>
-    <t>cafe sữa hạt</t>
-  </si>
-  <si>
-    <t>a05e1f24-38fa-4b1a-b5c0-c2101427dded</t>
-  </si>
-  <si>
-    <t>4489d58d-cf7b-49f6-a3f6-54915284f223</t>
-  </si>
-  <si>
-    <t>ef7205ac-9b18-4949-b04a-ea634d774841</t>
-  </si>
-  <si>
-    <t>phí ship</t>
-  </si>
-  <si>
-    <t>95232c93-a0e1-4596-ad9b-c3425e5f1699</t>
+    <t>Toppings</t>
+  </si>
+  <si>
+    <t>109a5a0e-0a30-426d-b2ec-f742ef01fd15</t>
+  </si>
+  <si>
+    <t>2026-02-01T02:51:36.4756835+00:00</t>
+  </si>
+  <si>
+    <t>Size M - Bạc Xỉu|SP000057|6000|bdf0dd62-999e-43a1-ad09-d3c0d4abb209</t>
+  </si>
+  <si>
+    <t>2ae9b0d6-ef2d-4069-806f-a5f11e326d9f</t>
+  </si>
+  <si>
+    <t>2026-02-01T02:52:06.2679857+00:00</t>
+  </si>
+  <si>
+    <t>Size L|SP000056|10000|71bcd18c-4a4b-4bf8-98d6-f4b8b4817213</t>
+  </si>
+  <si>
+    <t>4565424a-6343-4748-ab78-41174fddb4db</t>
+  </si>
+  <si>
+    <t>Size M|SP000055|5000|b9bd6435-a4f6-4eac-ad5f-adeffaace50a</t>
+  </si>
+  <si>
+    <t>1fb5cb15-4b94-492f-ac57-97ff8c5297a6</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:10:12.2940390+00:00</t>
+  </si>
+  <si>
+    <t>UpSize L|SP-00065|5000|ec676505-d248-4a18-9cd9-a6958914b713</t>
+  </si>
+  <si>
+    <t>8725529d-9554-469d-9826-78f3d55ee508</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:10:31.1470280+00:00</t>
+  </si>
+  <si>
+    <t>561ffcb9-2ee1-4e4e-8d76-3f959b81f113</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:10:59.8469926+00:00</t>
+  </si>
+  <si>
+    <t>ee55d594-89e4-4ec1-a73c-7ff9e4977509</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:10:59.8469943+00:00</t>
+  </si>
+  <si>
+    <t>768e8219-e676-416b-8578-75c2ecd9c581</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:11:09.5836800+00:00</t>
+  </si>
+  <si>
+    <t>b8f1a7c8-c7a8-424e-b4f4-097e51de7e4e</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:11:19.9475435+00:00</t>
+  </si>
+  <si>
+    <t>7e70a8d9-77da-449f-8123-690a50567211</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:11:54.3093819+00:00</t>
+  </si>
+  <si>
+    <t>22e15546-40ca-4d8e-b74b-ee3665a731d7</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:11:54.3093834+00:00</t>
+  </si>
+  <si>
+    <t>253c28e0-fbcf-41b5-b68b-dbe99ebfb9b2</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:12:55.3859353+00:00</t>
+  </si>
+  <si>
+    <t>ec6fef75-4d87-4f1d-8730-95ab563bd5e7</t>
+  </si>
+  <si>
+    <t>2026-02-01T03:13:07.0091819+00:00</t>
+  </si>
+  <si>
+    <t>d0f4bcb6-91dd-4ace-aeab-186cdc7ee79e</t>
+  </si>
+  <si>
+    <t>dd91d0a5-9697-4f04-910a-a15a90db1f84</t>
+  </si>
+  <si>
+    <t>2026-02-02T06:43:45.9416293+00:00</t>
   </si>
   <si>
     <t>email</t>
@@ -1920,7 +1791,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1960,94 +1831,14 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Order-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-    <tableStyle count="4" pivot="0" name="OrderItem-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -2073,49 +1864,6 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:P40" displayName="Bảng_1" name="Bảng_1" id="1">
-  <tableColumns count="16">
-    <tableColumn name="Id" id="1"/>
-    <tableColumn name="ClientOrderId" id="2"/>
-    <tableColumn name="CreatedAt" id="3"/>
-    <tableColumn name="OrderType" id="4"/>
-    <tableColumn name="TableNumber" id="5"/>
-    <tableColumn name="PaymentMethod" id="6"/>
-    <tableColumn name="CashAmount" id="7"/>
-    <tableColumn name="TransferAmount" id="8"/>
-    <tableColumn name="DiscountType" id="9"/>
-    <tableColumn name="DiscountValue" id="10"/>
-    <tableColumn name="DiscountAmount" id="11"/>
-    <tableColumn name="SubTotal" id="12"/>
-    <tableColumn name="Total" id="13"/>
-    <tableColumn name="Status" id="14"/>
-    <tableColumn name="Note" id="15"/>
-    <tableColumn name="IsActive" id="16"/>
-  </tableColumns>
-  <tableStyleInfo name="Order-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K64" displayName="Bảng_2" name="Bảng_2" id="2">
-  <tableColumns count="11">
-    <tableColumn name="OrderId" id="1"/>
-    <tableColumn name="ProductId" id="2"/>
-    <tableColumn name="Name" id="3"/>
-    <tableColumn name="UnitPrice" id="4"/>
-    <tableColumn name="Quantity" id="5"/>
-    <tableColumn name="DiscountType" id="6"/>
-    <tableColumn name="DiscountValue" id="7"/>
-    <tableColumn name="DiscountAmount" id="8"/>
-    <tableColumn name="Total" id="9"/>
-    <tableColumn name="Note" id="10"/>
-    <tableColumn name="IsActive" id="11"/>
-  </tableColumns>
-  <tableStyleInfo name="OrderItem-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2687,7 +2435,7 @@
         <v>0.0</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K11" s="7"/>
     </row>
@@ -2720,7 +2468,7 @@
         <v>0.0</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K12" s="7"/>
     </row>
@@ -2753,7 +2501,7 @@
         <v>0.0</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K13" s="7"/>
     </row>
@@ -5528,7 +5276,9 @@
       <c r="I105" s="5">
         <v>0.0</v>
       </c>
-      <c r="J105" s="7"/>
+      <c r="J105" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="K105" s="7"/>
     </row>
     <row r="106" hidden="1">
@@ -9855,1734 +9605,669 @@
     <col customWidth="1" min="16" max="16" width="14.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="13" t="s">
+    <row r="1">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+    <row r="2">
+      <c r="A2" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E2" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F2" s="16" t="s">
+      <c r="E2" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G2" s="15">
-        <v>33.0</v>
-      </c>
-      <c r="H2" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J2" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K2" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L2" s="15">
-        <v>33.0</v>
-      </c>
-      <c r="M2" s="15">
-        <v>33.0</v>
-      </c>
-      <c r="N2" s="16" t="s">
+      <c r="G2" s="12">
+        <v>88000.0</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="P2" s="17"/>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="J2" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="12">
+        <v>88000.0</v>
+      </c>
+      <c r="L2" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M2" s="12">
+        <v>88000.0</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="P2" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E3" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="E3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G3" s="15">
-        <v>33.0</v>
-      </c>
-      <c r="H3" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J3" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K3" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L3" s="15">
-        <v>33.0</v>
-      </c>
-      <c r="M3" s="15">
-        <v>33.0</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P3" s="17"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="G3" s="12">
+        <v>33000.0</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="12">
+        <v>33000.0</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M3" s="12">
+        <v>33000.0</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P3" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E4" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="E4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G4" s="15">
-        <v>36.0</v>
-      </c>
-      <c r="H4" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L4" s="15">
-        <v>36.0</v>
-      </c>
-      <c r="M4" s="15">
-        <v>36.0</v>
-      </c>
-      <c r="N4" s="16" t="s">
+      <c r="G4" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="P4" s="17"/>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="J4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="L4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M4" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P4" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E5" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F5" s="16" t="s">
+      <c r="E5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G5" s="15">
-        <v>36.0</v>
-      </c>
-      <c r="H5" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K5" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L5" s="15">
-        <v>36.0</v>
-      </c>
-      <c r="M5" s="15">
-        <v>36.0</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P5" s="17"/>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="G5" s="12">
+        <v>38000.0</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="12">
+        <v>38000.0</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M5" s="12">
+        <v>38000.0</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P5" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E6" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F6" s="16" t="s">
+      <c r="E6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G6" s="15">
-        <v>27.0</v>
-      </c>
-      <c r="H6" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J6" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L6" s="15">
-        <v>27.0</v>
-      </c>
-      <c r="M6" s="15">
-        <v>27.0</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P6" s="17"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>490</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="G6" s="12">
+        <v>31000.0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="12">
+        <v>31000.0</v>
+      </c>
+      <c r="L6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M6" s="12">
+        <v>31000.0</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P6" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E7" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F7" s="16" t="s">
+      <c r="E7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G7" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="H7" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="M7" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="N7" s="16" t="s">
+      <c r="G7" s="12">
+        <v>38000.0</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="P7" s="17"/>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="J7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="12">
+        <v>38000.0</v>
+      </c>
+      <c r="L7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M7" s="12">
+        <v>38000.0</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P7" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E8" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F8" s="16" t="s">
+      <c r="E8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G8" s="15">
-        <v>35.0</v>
-      </c>
-      <c r="H8" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="15">
-        <v>35.0</v>
-      </c>
-      <c r="M8" s="15">
-        <v>35.0</v>
-      </c>
-      <c r="N8" s="16" t="s">
+      <c r="G8" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="P8" s="17"/>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D9" s="14" t="s">
+      <c r="J8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P8" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E9" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="16" t="s">
+      <c r="E9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P9" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>66000.0</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="12">
+        <v>66000.0</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>66000.0</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P10" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>30000.0</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="12">
+        <v>30000.0</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="12">
+        <v>30000.0</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P11" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G9" s="15">
-        <v>21108.0</v>
-      </c>
-      <c r="H9" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="15">
-        <v>108.0</v>
-      </c>
-      <c r="M9" s="15">
-        <v>108.0</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P9" s="17"/>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="D10" s="14" t="s">
+      <c r="G12" s="12">
+        <v>32000.0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="12">
+        <v>32000.0</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="12">
+        <v>32000.0</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P12" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E10" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="G10" s="15">
-        <v>41.0</v>
-      </c>
-      <c r="H10" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="J10" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="15">
-        <v>43.0</v>
-      </c>
-      <c r="M10" s="15">
-        <v>43.0</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="O10" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="P10" s="17"/>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>501</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>502</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="D11" s="14" t="s">
+      <c r="E13" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>162000.0</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="12">
+        <v>162000.0</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="12">
+        <v>162000.0</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P13" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="E11" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F11" s="16" t="s">
+      <c r="E14" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="G11" s="15">
-        <v>20.0</v>
-      </c>
-      <c r="H11" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="15">
-        <v>20.0</v>
-      </c>
-      <c r="M11" s="15">
-        <v>20.0</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P11" s="17"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>504</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E12" s="15">
-        <v>4.0</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G12" s="15">
-        <v>27.0</v>
-      </c>
-      <c r="H12" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="15">
-        <v>27.0</v>
-      </c>
-      <c r="M12" s="15">
-        <v>27.0</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P12" s="17"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E13" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G13" s="15">
-        <v>20.0</v>
-      </c>
-      <c r="H13" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L13" s="15">
-        <v>20.0</v>
-      </c>
-      <c r="M13" s="15">
-        <v>20.0</v>
-      </c>
-      <c r="N13" s="16" t="s">
+      <c r="G14" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="P13" s="17"/>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E14" s="15">
-        <v>4.0</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G14" s="15">
-        <v>216.0</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="15">
-        <v>216.0</v>
-      </c>
-      <c r="M14" s="15">
-        <v>216.0</v>
-      </c>
-      <c r="N14" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P14" s="17"/>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>510</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>511</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>512</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G15" s="15">
-        <v>68.0</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="15">
-        <v>68.0</v>
-      </c>
-      <c r="M15" s="15">
-        <v>68.0</v>
-      </c>
-      <c r="N15" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P15" s="17"/>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>513</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E16" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="G16" s="15">
-        <v>18000.0</v>
-      </c>
-      <c r="H16" s="15">
-        <v>50000.0</v>
-      </c>
-      <c r="J16" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="15">
-        <v>68000.0</v>
-      </c>
-      <c r="M16" s="15">
-        <v>68000.0</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P16" s="17"/>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>517</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>518</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E17" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="G17" s="15">
-        <v>12000.0</v>
-      </c>
-      <c r="H17" s="15">
-        <v>5000.0</v>
-      </c>
-      <c r="J17" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="M17" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P17" s="17"/>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E18" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="G18" s="15">
-        <v>18000.0</v>
-      </c>
-      <c r="H18" s="15">
-        <v>50000.0</v>
-      </c>
-      <c r="J18" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="15">
-        <v>68000.0</v>
-      </c>
-      <c r="M18" s="15">
-        <v>68000.0</v>
-      </c>
-      <c r="N18" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P18" s="17"/>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>522</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>523</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E19" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G19" s="15">
-        <v>108000.0</v>
-      </c>
-      <c r="H19" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="15">
-        <v>108000.0</v>
-      </c>
-      <c r="M19" s="15">
-        <v>108000.0</v>
-      </c>
-      <c r="N19" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P19" s="17"/>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>527</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E20" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>528</v>
-      </c>
-      <c r="G20" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="15">
-        <v>87000.0</v>
-      </c>
-      <c r="J20" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="15">
-        <v>87000.0</v>
-      </c>
-      <c r="M20" s="15">
-        <v>87000.0</v>
-      </c>
-      <c r="N20" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P20" s="17"/>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E21" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>528</v>
-      </c>
-      <c r="G21" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="15">
-        <v>111200.0</v>
-      </c>
-      <c r="J21" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="15">
-        <v>139000.0</v>
-      </c>
-      <c r="M21" s="15">
-        <v>139000.0</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P21" s="17"/>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E22" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G22" s="15">
-        <v>80000.0</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="15">
-        <v>80000.0</v>
-      </c>
-      <c r="M22" s="15">
-        <v>80000.0</v>
-      </c>
-      <c r="N22" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P22" s="17"/>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E23" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G23" s="15">
-        <v>71000.0</v>
-      </c>
-      <c r="H23" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="15">
-        <v>71000.0</v>
-      </c>
-      <c r="M23" s="15">
-        <v>71000.0</v>
-      </c>
-      <c r="N23" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="O23" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="P23" s="17"/>
-    </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>541</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E24" s="15">
-        <v>5.0</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G24" s="15">
-        <v>81000.0</v>
-      </c>
-      <c r="H24" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J24" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="15">
-        <v>81000.0</v>
-      </c>
-      <c r="M24" s="15">
-        <v>81000.0</v>
-      </c>
-      <c r="N24" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P24" s="17"/>
-    </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E25" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G25" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="H25" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="M25" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="N25" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P25" s="17"/>
-    </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E26" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G26" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="H26" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J26" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="M26" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="N26" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P26" s="17"/>
-    </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>549</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>550</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E27" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G27" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="H27" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="M27" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="N27" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P27" s="17"/>
-    </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="14" t="s">
-        <v>551</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>553</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E28" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="G28" s="15">
-        <v>45450.0</v>
-      </c>
-      <c r="H28" s="15">
-        <v>5550.0</v>
-      </c>
-      <c r="J28" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="15">
-        <v>51000.0</v>
-      </c>
-      <c r="M28" s="15">
-        <v>51000.0</v>
-      </c>
-      <c r="N28" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P28" s="17"/>
-    </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>555</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>556</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G29" s="15">
-        <v>117000.0</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J29" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="15">
-        <v>117000.0</v>
-      </c>
-      <c r="M29" s="15">
-        <v>117000.0</v>
-      </c>
-      <c r="N29" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P29" s="17"/>
-    </row>
-    <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>558</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>559</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G30" s="15">
-        <v>46000.0</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J30" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="15">
-        <v>46000.0</v>
-      </c>
-      <c r="M30" s="15">
-        <v>46000.0</v>
-      </c>
-      <c r="N30" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P30" s="17"/>
-    </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="14" t="s">
-        <v>560</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>561</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>562</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E31" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G31" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J31" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L31" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="M31" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="N31" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P31" s="17"/>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>564</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>565</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E32" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G32" s="15">
-        <v>344000.0</v>
-      </c>
-      <c r="H32" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="15">
-        <v>344000.0</v>
-      </c>
-      <c r="M32" s="15">
-        <v>344000.0</v>
-      </c>
-      <c r="N32" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P32" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="14" t="s">
-        <v>566</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E33" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G33" s="15">
-        <v>22000.0</v>
-      </c>
-      <c r="H33" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="15">
-        <v>22000.0</v>
-      </c>
-      <c r="M33" s="15">
-        <v>22000.0</v>
-      </c>
-      <c r="N33" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P33" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="14" t="s">
-        <v>569</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>570</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>571</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E34" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G34" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="H34" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="M34" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="N34" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P34" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>574</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E35" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G35" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="H35" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="M35" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="N35" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P35" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>577</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E36" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G36" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="H36" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="M36" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="N36" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P36" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>579</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>580</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E37" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="G37" s="15">
-        <v>24000.0</v>
-      </c>
-      <c r="H37" s="15">
-        <v>50000.0</v>
-      </c>
-      <c r="J37" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K37" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L37" s="15">
-        <v>74000.0</v>
-      </c>
-      <c r="M37" s="15">
-        <v>74000.0</v>
-      </c>
-      <c r="N37" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P37" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="14" t="s">
-        <v>581</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>582</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>583</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E38" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G38" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="H38" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J38" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K38" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="M38" s="15">
-        <v>17000.0</v>
-      </c>
-      <c r="N38" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P38" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="14" t="s">
-        <v>584</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>585</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>586</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E39" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G39" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="H39" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J39" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K39" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="M39" s="15">
-        <v>20000.0</v>
-      </c>
-      <c r="N39" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="P39" s="15">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>588</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>589</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="E40" s="15">
-        <v>5.0</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="G40" s="15">
-        <v>132600.0</v>
-      </c>
-      <c r="H40" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J40" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K40" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L40" s="15">
-        <v>156000.0</v>
-      </c>
-      <c r="M40" s="15">
-        <v>156000.0</v>
-      </c>
-      <c r="N40" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="P40" s="15">
+      <c r="J14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="L14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="M14" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="P14" s="12">
         <v>1.0</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F40">
-      <formula1>"CASH,COMBINED,TRANSFER"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="N2:N40">
-      <formula1>"DRAFT,SUCCESS"</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E40 G2:H40 J2:M40 P2:P40">
-      <formula1>AND(ISNUMBER(E2),(NOT(OR(NOT(ISERROR(DATEVALUE(E2))), AND(ISNUMBER(E2), LEFT(CELL("format", E2))="D")))))</formula1>
-    </dataValidation>
-  </dataValidations>
   <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -11593,1750 +10278,620 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="48.13"/>
-    <col customWidth="1" min="2" max="2" width="33.63"/>
-    <col customWidth="1" min="3" max="3" width="21.5"/>
-    <col customWidth="1" min="6" max="6" width="15.63"/>
-    <col customWidth="1" min="7" max="7" width="16.25"/>
-    <col customWidth="1" min="8" max="8" width="18.0"/>
-    <col customWidth="1" min="10" max="10" width="4.5"/>
+    <col customWidth="1" min="1" max="2" width="48.13"/>
+    <col customWidth="1" min="3" max="4" width="33.63"/>
+    <col customWidth="1" min="5" max="5" width="21.5"/>
+    <col customWidth="1" min="8" max="8" width="15.63"/>
+    <col customWidth="1" min="9" max="9" width="16.25"/>
+    <col customWidth="1" min="10" max="10" width="18.0"/>
+    <col customWidth="1" min="12" max="12" width="50.75"/>
+    <col customWidth="1" min="13" max="13" width="21.13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>590</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>591</v>
+    <row r="1">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>521</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>592</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>593</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="L1" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="M1" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+    <row r="2">
+      <c r="A2" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I2" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J2" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="12">
+        <v>33000.0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="N2" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="12">
+        <v>17000.0</v>
+      </c>
+      <c r="G3" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="N3" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="D2" s="14">
-        <v>33.0</v>
-      </c>
-      <c r="E2" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H2" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I2" s="14">
-        <v>33.0</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>483</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="D3" s="14">
-        <v>33.0</v>
-      </c>
-      <c r="E3" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G3" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="14">
-        <v>33.0</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="D4" s="14">
-        <v>36.0</v>
-      </c>
-      <c r="E4" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G4" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="14">
-        <v>36.0</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="D5" s="14">
-        <v>36.0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="14">
-        <v>36.0</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="D6" s="14">
-        <v>27.0</v>
-      </c>
-      <c r="E6" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="14">
-        <v>27.0</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="C4" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="12">
+        <v>17000.0</v>
+      </c>
+      <c r="G4" s="12">
+        <v>4.0</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="12">
+        <v>88000.0</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="N4" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="D7" s="14">
-        <v>7.0</v>
-      </c>
-      <c r="E7" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="14">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="D8" s="14">
-        <v>7.0</v>
-      </c>
-      <c r="E8" s="14">
-        <v>5.0</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="14">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="14" t="s">
-        <v>596</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="14">
-        <v>36.0</v>
-      </c>
-      <c r="E9" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="G9" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="14">
-        <v>108.0</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="D10" s="14">
-        <v>36.0</v>
-      </c>
-      <c r="E10" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="G10" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="14">
-        <v>108.0</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>597</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>598</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="D11" s="14">
-        <v>68.0</v>
-      </c>
-      <c r="E11" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G11" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="14">
-        <v>68.0</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>600</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>598</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="D12" s="14">
-        <v>68.0</v>
-      </c>
-      <c r="E12" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="14">
-        <v>68.0</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="C5" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="12">
+        <v>33000.0</v>
+      </c>
+      <c r="G5" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="12">
+        <v>38000.0</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="N5" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="12">
+        <v>31000.0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="12">
+        <v>31000.0</v>
+      </c>
+      <c r="N6" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="D13" s="14">
-        <v>7.0</v>
-      </c>
-      <c r="E13" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="14">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="14" t="s">
+      <c r="C7" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="12">
+        <v>32000.0</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="N7" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="14">
-        <v>36.0</v>
-      </c>
-      <c r="E14" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="14">
-        <v>36.0</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>501</v>
-      </c>
-      <c r="B15" s="14" t="s">
+      <c r="C8" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="F8" s="12">
+        <v>6000.0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="12">
+        <v>6000.0</v>
+      </c>
+      <c r="N8" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="14">
-        <v>20.0</v>
-      </c>
-      <c r="E15" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="14">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="B16" s="14" t="s">
+      <c r="F9" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="N9" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="14">
-        <v>27.0</v>
-      </c>
-      <c r="E16" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="14">
-        <v>27.0</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="B17" s="14" t="s">
+      <c r="F10" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="N10" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="12">
+        <v>31000.0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="12">
+        <v>36000.0</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="N11" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="14">
-        <v>20.0</v>
-      </c>
-      <c r="E17" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="14">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="14">
-        <v>27.0</v>
-      </c>
-      <c r="E18" s="14">
-        <v>8.0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="14">
-        <v>216.0</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>510</v>
-      </c>
-      <c r="B19" s="14" t="s">
+      <c r="F12" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="12">
+        <v>30000.0</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="N12" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="12">
+        <v>20000.0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="12">
+        <v>30000.0</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="N13" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F14" s="12">
+        <v>27000.0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="12">
+        <v>32000.0</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="N14" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="14">
-        <v>17.0</v>
-      </c>
-      <c r="E19" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="G19" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="14">
-        <v>68.0</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="14" t="s">
-        <v>513</v>
-      </c>
-      <c r="B20" s="14" t="s">
+      <c r="F15" s="12">
+        <v>17000.0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>6.0</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="12">
+        <v>162000.0</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="N15" s="12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="14">
+      <c r="F16" s="12">
         <v>17000.0</v>
       </c>
-      <c r="E20" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="14">
-        <v>68000.0</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E21" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G21" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="14">
-        <v>17000.0</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E22" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="G22" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="14">
-        <v>68000.0</v>
-      </c>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="14" t="s">
-        <v>522</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="G16" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="12">
         <v>27000.0</v>
       </c>
-      <c r="E23" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="G23" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="14">
-        <v>108000.0</v>
-      </c>
-    </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E24" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G24" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="14">
-        <v>27000.0</v>
-      </c>
-    </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E25" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="14">
-        <v>27000.0</v>
-      </c>
-    </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="14">
-        <v>33000.0</v>
-      </c>
-      <c r="E26" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="14">
-        <v>33000.0</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E27" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="G27" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="14">
-        <v>108000.0</v>
-      </c>
-    </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="14">
-        <v>31000.0</v>
-      </c>
-      <c r="E28" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G28" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H28" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="14">
-        <v>31000.0</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E29" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G29" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H29" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I29" s="14">
-        <v>27000.0</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E30" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G30" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H30" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I30" s="14">
-        <v>27000.0</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="14">
-        <v>26000.0</v>
-      </c>
-      <c r="E31" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G31" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H31" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I31" s="14">
-        <v>26000.0</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E32" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G32" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="14">
-        <v>17000.0</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E33" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="14">
-        <v>27000.0</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E34" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G34" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="14">
-        <v>27000.0</v>
-      </c>
-    </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E35" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G35" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="14">
-        <v>27000.0</v>
-      </c>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E36" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="G36" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="14">
-        <v>54000.0</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E37" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G37" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I37" s="14">
-        <v>17000.0</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="E38" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G38" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H38" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I38" s="14">
-        <v>20000.0</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E39" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H39" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="14">
-        <v>17000.0</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="14" t="s">
-        <v>551</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E40" s="14">
-        <v>3.0</v>
-      </c>
-      <c r="G40" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H40" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I40" s="14">
-        <v>51000.0</v>
-      </c>
-    </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E41" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G41" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H41" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I41" s="14">
-        <v>17000.0</v>
-      </c>
-    </row>
-    <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="E42" s="14">
-        <v>5.0</v>
-      </c>
-      <c r="G42" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H42" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I42" s="14">
-        <v>100000.0</v>
-      </c>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="E43" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G43" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H43" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I43" s="14">
-        <v>20000.0</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D44" s="14">
-        <v>26000.0</v>
-      </c>
-      <c r="E44" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G44" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H44" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I44" s="14">
-        <v>26000.0</v>
-      </c>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="14" t="s">
-        <v>560</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="E45" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G45" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H45" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I45" s="14">
-        <v>20000.0</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E46" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G46" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H46" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I46" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="K46" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="E47" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G47" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H47" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I47" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="K47" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E48" s="14">
-        <v>5.0</v>
-      </c>
-      <c r="G48" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H48" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I48" s="14">
-        <v>135000.0</v>
-      </c>
-      <c r="K48" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D49" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E49" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G49" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H49" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I49" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="K49" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D50" s="14">
-        <v>31000.0</v>
-      </c>
-      <c r="E50" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G50" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H50" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I50" s="14">
-        <v>31000.0</v>
-      </c>
-      <c r="K50" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" s="14">
-        <v>26000.0</v>
-      </c>
-      <c r="E51" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G51" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H51" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I51" s="14">
-        <v>26000.0</v>
-      </c>
-      <c r="K51" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>372</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="D52" s="14">
-        <v>26000.0</v>
-      </c>
-      <c r="E52" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G52" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H52" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I52" s="14">
-        <v>26000.0</v>
-      </c>
-      <c r="K52" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="14">
-        <v>33000.0</v>
-      </c>
-      <c r="E53" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G53" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H53" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I53" s="14">
-        <v>33000.0</v>
-      </c>
-      <c r="K53" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="D54" s="14">
-        <v>29000.0</v>
-      </c>
-      <c r="E54" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G54" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H54" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I54" s="14">
-        <v>29000.0</v>
-      </c>
-      <c r="K54" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="14" t="s">
-        <v>566</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E55" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G55" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H55" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I55" s="14">
-        <v>22000.0</v>
-      </c>
-      <c r="K55" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="14" t="s">
-        <v>569</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E56" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G56" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H56" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I56" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="K56" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E57" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G57" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H57" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I57" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="K57" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="E58" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G58" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H58" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I58" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="K58" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D59" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="E59" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G59" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H59" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I59" s="14">
-        <v>20000.0</v>
-      </c>
-      <c r="K59" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D60" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E60" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G60" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H60" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I60" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="K60" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D61" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E61" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G61" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H61" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I61" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="K61" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="14" t="s">
-        <v>581</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="E62" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="G62" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H62" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I62" s="14">
-        <v>17000.0</v>
-      </c>
-      <c r="K62" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E63" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="G63" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H63" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I63" s="14">
-        <v>156000.0</v>
-      </c>
-      <c r="K63" s="14">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D64" s="14">
-        <v>27000.0</v>
-      </c>
-      <c r="E64" s="14">
-        <v>4.0</v>
-      </c>
-      <c r="G64" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="H64" s="14">
-        <v>0.0</v>
-      </c>
-      <c r="I64" s="14">
-        <v>156000.0</v>
-      </c>
-      <c r="K64" s="14">
+      <c r="L16" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="N16" s="12">
         <v>1.0</v>
       </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -13356,16 +10911,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>601</v>
+        <v>558</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>602</v>
+        <v>559</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>603</v>
+        <v>560</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>604</v>
+        <v>561</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>7</v>
@@ -13376,16 +10931,16 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>605</v>
+        <v>562</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>606</v>
+        <v>563</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>607</v>
+        <v>564</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>608</v>
+        <v>565</v>
       </c>
       <c r="F2" s="12">
         <v>1.0</v>
@@ -13396,16 +10951,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>609</v>
+        <v>566</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>610</v>
+        <v>567</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>611</v>
+        <v>568</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>612</v>
+        <v>569</v>
       </c>
       <c r="F3" s="12">
         <v>1.0</v>
